--- a/output/pdf_financials_xlsx/W.xlsx
+++ b/output/pdf_financials_xlsx/W.xlsx
@@ -6236,43 +6236,43 @@
         <v>1.309342</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.73751</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.738157</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.738157</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.838157</v>
       </c>
       <c r="R92" s="3" t="n">
         <v>1.838157</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.497951</v>
       </c>
     </row>
     <row r="119">
@@ -11476,7 +11476,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -14018,7 +14022,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -15986,7 +15994,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -18292,7 +18304,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19988,7 +20004,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -21680,7 +21700,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -22324,7 +22348,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -26070,7 +26098,11 @@
           <t>Reserves 7 1,737,510</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -30178,7 +30210,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/W.xlsx
+++ b/output/pdf_financials_xlsx/W.xlsx
@@ -2565,58 +2565,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.199534</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.050713</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050713</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.49354</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.101014</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.025044</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00615</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.031402</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00596</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.085353</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.102881</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.063523</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.021063</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.182677</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.135161</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.07778500000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.025371</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.866491</v>
       </c>
     </row>
     <row r="35">
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.200784</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.069463</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.070713</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.49354</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.101014</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.025044</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.00615</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.031402</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00596</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.085353</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.102881</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.063523</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.021063</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.182677</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.135161</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.07778500000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.025371</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.866491</v>
       </c>
     </row>
     <row r="37">
@@ -3419,28 +3419,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.699354</v>
+        <v>0.49982</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.250713</v>
+        <v>0.2</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.251955</v>
+        <v>0.201242</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.500233</v>
+        <v>0.006693</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.104764</v>
+        <v>0.00375</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.025044</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00615</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.044116</v>
+        <v>0.012714</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.025371</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.236002</v>
+        <v>0.369511</v>
       </c>
     </row>
     <row r="49">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">

--- a/output/pdf_financials_xlsx/W.xlsx
+++ b/output/pdf_financials_xlsx/W.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.412653</v>
+        <v>0.463653</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.305968</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.488725</v>
+        <v>0.539725</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.325179</v>
@@ -7453,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.041955</v>
       </c>
     </row>
     <row r="112">
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.041955</v>
       </c>
     </row>
     <row r="135">
@@ -9125,7 +9125,7 @@
         <v>-0.052414</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-1.108842</v>
+        <v>-1.150797</v>
       </c>
     </row>
   </sheetData>
@@ -30104,7 +30104,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -33646,7 +33650,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -36070,7 +36078,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -36802,7 +36814,11 @@
           <t>Gross proceeds from private placement</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -38394,7 +38410,11 @@
           <t>Gross proceeds from private placement</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -51454,7 +51474,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E403" s="5" t="n">
         <v>0.051</v>
       </c>
